--- a/templates/공정명마스터_양식.xlsx
+++ b/templates/공정명마스터_양식.xlsx
@@ -479,11 +479,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -497,6 +498,11 @@
           <t>공정명</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>COPQ제외여부</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -509,6 +515,11 @@
           <t>성형</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -521,6 +532,11 @@
           <t>소결</t>
         </is>
       </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -533,6 +549,11 @@
           <t>선별</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -545,6 +566,11 @@
           <t>성형</t>
         </is>
       </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -557,6 +583,11 @@
           <t>소결</t>
         </is>
       </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -569,6 +600,11 @@
           <t>정형</t>
         </is>
       </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -581,11 +617,19 @@
           <t>선별</t>
         </is>
       </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="파트구분 오류" error="VMS PART 또는 TM PART만 입력 가능합니다." type="list">
       <formula1>"VMS PART,TM PART"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="COPQ제외여부 오류" error="Y 또는 N만 입력 가능합니다." type="list">
+      <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -598,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B14"/>
+  <dimension ref="B2:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -648,42 +692,56 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>· COPQ제외여부 : Y이면 이 공정에 배분된 공정불량·셋팅불량 비용을 COPQ 계산의 Scrap Cost에서 제외합니다. (성형공정 = Y, 빈칸은 N으로 처리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>※ COPQ제외여부가 Y여도 KPI의 Scrap Cost(전체 금액)에는 포함됩니다. COPQ 계산에서만 제외됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="5" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>· 같은 파트 안에서 공정명 중복 금지.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>· 제품 MASTER / 불량유형 MASTER에 쓰는 공정명은 반드시 이 목록에 있어야 합니다 (업로드 시 검증).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>※ 2행부터의 데이터는 '작성 예시'입니다. 실제 데이터로 교체(또는 삭제 후 입력)하여 업로드하세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
+          <t>· 제품 MASTER / 불량유형 MASTER에 쓰는 공정명은 반드시 이 목록에 있어야 합니다 (업로드 시 검증).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>※ 2행부터의 데이터는 '작성 예시'입니다. 실제 데이터로 교체(또는 삭제 후 입력)하여 업로드하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>· 1행(제목 행)은 수정/삭제하지 마세요. 시스템이 열 이름으로 데이터를 인식합니다.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="5" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>· 시트 이름(DATA)도 변경하지 마세요.</t>
         </is>
